--- a/Lasser_Driver_v5/AC_Board/AC_Board_BOM_digikey_priced.xlsx
+++ b/Lasser_Driver_v5/AC_Board/AC_Board_BOM_digikey_priced.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1757255</t>
+          <t>1729131</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -557,27 +557,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>J1,J2,J3</t>
+          <t>AC_Board J1,J2,J3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MSTBA 2,5/3-G-5,08</t>
+          <t>MKDS 1,5/3-5,08</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Phoenix_MSTBA_3</t>
+          <t>TerminalBlock_MKDS_3_P5.08mm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Term block header 3pos 5.08mm horiz</t>
+          <t>Single-piece PCB screw terminal 3pos 5.08mm side-entry</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>277-1107-ND</t>
+          <t>277-1248-ND</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11325</v>
+        <v>15236</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.9</v>
+        <v>1.44</v>
       </c>
       <c r="O2" s="2">
         <f>N2*L2</f>
@@ -608,7 +608,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://www.phoenixcontact.com/us/products/1757255/pdf</t>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/5784/MKDSN%201%2C5_%203-5%2C08.pdf</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PEM01</t>
+          <t>AC_Board PEM01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PEM01 fuse</t>
+          <t>AC_Board PEM01 fuse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>AC_Board R1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>953846</v>
+        <v>953696</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>AC_Board T1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>AC_Board T2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TH1</t>
+          <t>AC_Board TH1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Prices pulled 2026-06-30 14:34 (USD), 1 board(s)</t>
+          <t>Prices pulled 2026-06-30 15:06 (USD), 1 board(s)</t>
         </is>
       </c>
     </row>
